--- a/public/StructureDefinition-pghd-blood-glucose.xlsx
+++ b/public/StructureDefinition-pghd-blood-glucose.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T16:46:43-05:00</t>
+    <t>2026-04-23T16:43:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-blood-glucose.xlsx
+++ b/public/StructureDefinition-pghd-blood-glucose.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T16:43:45-05:00</t>
+    <t>2026-04-23T17:08:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-blood-glucose.xlsx
+++ b/public/StructureDefinition-pghd-blood-glucose.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3946" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3946" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T17:08:04-05:00</t>
+    <t>2026-06-11T13:06:45-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1289,10 +1289,6 @@
     <t>Observation.value[x].extension.id</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Observation.value[x].extension:alternativeQuantity.extension</t>
   </si>
   <si>
@@ -1335,14 +1331,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Observation.value[x].extension:alternativeQuantity.value[x].id</t>
@@ -9416,7 +9408,7 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>95</v>
+        <v>206</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>207</v>
@@ -9482,7 +9474,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>82</v>
@@ -9508,10 +9500,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9537,10 +9529,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9626,10 +9618,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9655,13 +9647,13 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9669,49 +9661,49 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>93</v>
@@ -9746,10 +9738,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9775,10 +9767,10 @@
         <v>389</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9829,7 +9821,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9838,7 +9830,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9864,10 +9856,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9982,10 +9974,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10102,10 +10094,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10128,19 +10120,19 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10189,7 +10181,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10210,10 +10202,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10224,10 +10216,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10253,20 +10245,20 @@
         <v>113</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>82</v>
@@ -10290,28 +10282,28 @@
         <v>182</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10332,10 +10324,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10346,10 +10338,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10375,21 +10367,21 @@
         <v>206</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10431,7 +10423,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10452,10 +10444,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10466,10 +10458,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10495,72 +10487,72 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI68" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10572,10 +10564,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10586,10 +10578,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10615,23 +10607,23 @@
         <v>113</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10673,7 +10665,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10694,10 +10686,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10708,10 +10700,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10734,19 +10726,19 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10795,7 +10787,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10816,10 +10808,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10830,10 +10822,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10859,20 +10851,20 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q71" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>82</v>
@@ -10896,28 +10888,28 @@
         <v>182</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10938,10 +10930,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10952,10 +10944,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10981,21 +10973,21 @@
         <v>206</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>82</v>
@@ -11037,7 +11029,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11058,10 +11050,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11072,10 +11064,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11101,72 +11093,72 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11178,10 +11170,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11192,10 +11184,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11221,23 +11213,23 @@
         <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -11279,7 +11271,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11300,10 +11292,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11314,10 +11306,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11343,16 +11335,16 @@
         <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11377,40 +11369,40 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI75" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11425,7 +11417,7 @@
         <v>136</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11436,14 +11428,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11465,16 +11457,16 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11499,13 +11491,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11523,7 +11515,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11541,27 +11533,27 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11584,19 +11576,19 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11645,7 +11637,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11666,10 +11658,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11680,10 +11672,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11709,13 +11701,13 @@
         <v>191</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11744,10 +11736,10 @@
         <v>291</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11765,7 +11757,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11783,27 +11775,27 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11829,16 +11821,16 @@
         <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11866,10 +11858,10 @@
         <v>291</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11887,7 +11879,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11908,10 +11900,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11922,10 +11914,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11948,16 +11940,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12007,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12025,27 +12017,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12068,16 +12060,16 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12127,7 +12119,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12145,27 +12137,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12188,19 +12180,19 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12249,7 +12241,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12261,19 +12253,19 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12284,10 +12276,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12402,10 +12394,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12522,14 +12514,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12551,10 +12543,10 @@
         <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>142</v>
@@ -12609,7 +12601,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12644,10 +12636,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12670,13 +12662,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12727,7 +12719,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12736,7 +12728,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12748,10 +12740,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12762,10 +12754,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12788,13 +12780,13 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12845,7 +12837,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12854,7 +12846,7 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -12866,10 +12858,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12880,10 +12872,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12909,16 +12901,16 @@
         <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12946,10 +12938,10 @@
         <v>117</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12967,7 +12959,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12985,13 +12977,13 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13002,10 +12994,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13031,16 +13023,16 @@
         <v>191</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13068,10 +13060,10 @@
         <v>291</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13089,7 +13081,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13107,13 +13099,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13124,10 +13116,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13150,17 +13142,17 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13209,7 +13201,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13233,7 +13225,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13244,10 +13236,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13273,10 +13265,10 @@
         <v>206</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13327,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13348,10 +13340,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13362,10 +13354,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13388,16 +13380,16 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13447,7 +13439,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13468,10 +13460,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13482,10 +13474,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13508,16 +13500,16 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13567,7 +13559,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13588,10 +13580,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13602,10 +13594,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13628,19 +13620,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13689,7 +13681,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13710,10 +13702,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13724,10 +13716,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13842,10 +13834,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13962,14 +13954,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13991,10 +13983,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>142</v>
@@ -14049,7 +14041,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14084,10 +14076,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14113,13 +14105,13 @@
         <v>191</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>290</v>
@@ -14171,7 +14163,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>93</v>
@@ -14189,7 +14181,7 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>296</v>
@@ -14206,10 +14198,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14232,16 +14224,16 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>391</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>393</v>
@@ -14293,7 +14285,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14311,7 +14303,7 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>396</v>
@@ -14328,10 +14320,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14357,16 +14349,16 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>641</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14391,40 +14383,40 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>105</v>
@@ -14439,7 +14431,7 @@
         <v>136</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14450,14 +14442,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14479,16 +14471,16 @@
         <v>191</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14513,13 +14505,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14537,7 +14529,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14555,27 +14547,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14601,16 +14593,16 @@
         <v>83</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14659,7 +14651,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14680,10 +14672,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>

--- a/public/StructureDefinition-pghd-blood-glucose.xlsx
+++ b/public/StructureDefinition-pghd-blood-glucose.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:06:45-06:00</t>
+    <t>2026-06-11T16:28:41-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
